--- a/curriculum_mapping_2026-27/CurriculumMapping_Geo_4_To_check.xlsx
+++ b/curriculum_mapping_2026-27/CurriculumMapping_Geo_4_To_check.xlsx
@@ -11,11 +11,13 @@
     <sheet name="Geography BA" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Geography BSc" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Rows removed (not usable)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Unverified modules" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geography BA'!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geography BA'!$A$1:$K$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Geography BSc'!$A$1:$K$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rows removed (not usable)'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rows removed (not usable)'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Unverified modules'!$A$1:$K$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47,7 +49,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -61,8 +63,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,23 +105,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -477,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -555,7 +573,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Seoul National University</t>
+          <t>Hong Kong University of Science and Technology</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -564,29 +582,29 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Fall 2026 (SNU 2nd semester) checked from the SNU course list: the Geography Department offers only ONE English-taught undergraduate course (208.407A The Politics of Space and Geopolitics); all other geography courses, including the handbook ones (208.302 Geography of Korea, 208.421A History of Geographical Space and Thoughts, 205.242A Population Change and Aging Society), are taught in Korean. 2 English-taught usable modules found, 4 needed -&gt; NOT enough for Fall 2026. Spring 2027 (1st semester) list not yet checked.</t>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Meets the minimum only if 6 module(s) with UNVERIFIED terms run in the partner semester (3 confirmed + 6 unverified, 4 needed). Check the 2026/27 timetable.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Spring Semester 1 (Mar-Jun - UoL Semester 2) OR Fall Semester 2 (Sep-Dec - UoL Semester 1)</t>
+          <t xml:space="preserve">Semester 1 or 2 </t>
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -597,7 +615,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -629,38 +647,38 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>University of Groningen</t>
+          <t>Seoul National University</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Faculty access: confirmed list says UoL students apply to Faculty of Arts / Science and Engineering, but most usable modules are Faculty of Spatial Sciences (FSS does run an exchange course, GESPSP2). Confirm with Study Abroad. Also the workbook's original Groningen rows are Semester 1 (wrong term).</t>
+          <t>Fall 2026 (SNU 2nd semester) checked from the SNU course list: the Geography Department offers only ONE English-taught undergraduate course (208.407A The Politics of Space and Geopolitics); all other geography courses, including the handbook ones (208.302 Geography of Korea, 208.421A History of Geographical Space and Thoughts, 205.242A Population Change and Aging Society), are taught in Korean. 2 English-taught usable modules found, 4 needed -&gt; NOT enough for Fall 2026. Spring 2027 (1st semester) list not yet checked.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Semester 2</t>
+          <t>Spring Semester 1 (Mar-Jun - UoL Semester 2) OR Fall Semester 2 (Sep-Dec - UoL Semester 1)</t>
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -671,11 +689,11 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -694,21 +712,21 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Vrije Universiteit Amsterdam</t>
+          <t>University of Groningen</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Geography BA</t>
+          <t>Geography BSc</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -718,11 +736,11 @@
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>6 English-taught modules in Semester 2 (P4-P6), 5 needed (30 EC). AB_1318 and AB_1271 removed: taught in Dutch (all other rows checked: English). Minimum met. Confirm exchange access with VU International Office.</t>
+          <t>Faculty access: confirmed list says UoL students apply to Faculty of Arts / Science and Engineering, but most usable modules are Faculty of Spatial Sciences (FSS does run an exchange course, GESPSP2). Confirm with Study Abroad. Also the workbook's original Groningen rows are Semester 1 (wrong term).</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -734,7 +752,7 @@
         <v>6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -745,11 +763,11 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Geography BSc</t>
+          <t>Geography BA</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -759,18 +777,55 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
+          <t>6 English-taught modules in Semester 2 (P4-P6), 5 needed (30 EC). AB_1318 and AB_1271 removed: taught in Dutch (all other rows checked: English). Minimum met. Confirm exchange access with VU International Office.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Semester 2</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t>4 English-taught modules in Semester 2 (P4-P6), 5 needed (30 EC). AB_1318 and AB_1271 removed: taught in Dutch (all other rows checked: English). NOT enough - short by 1. Confirm exchange access with VU International Office.</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Semester 2</t>
         </is>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H11" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I11" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -785,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -802,225 +857,225 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>University name and country</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Programme title</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>UoL module code and title</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>UoL module level</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Host uni module code and title</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Host uni module level</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Core or optional</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Semester</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>CB approval</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Evidence / source URL</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Check notes (Oct 2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Seoul National University — South Korea</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>208.407A The Politics of Space and Geopolitics (3 credits)</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>ENVR2020 Urban Air Pollution (3 credits)</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Fall 2026 - HKUST takes students in either semester</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/ENVR | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM VERIFIED Oct 2026: Fall 2026 - HKUST takes students in either semester [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>ENVR2060 From Trash to Treasure: Transforming Waste into Resources (3 credits)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2026-27 catalogue (term set at registration)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/ENVR | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM NOT VERIFIED: Not in Fall 2026 schedule; Spring 2027 schedule not yet published (HKUST takes either semester) [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>ENVR3005 Environmental Risks: Principles and Practices (3 credits)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026 (SNU 2nd semester, Sep-Dec) - English-taught</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>Host: https://sugang.snu.ac.kr/ (SNU Course Search export, 2026 2nd semester (Fall, Sep-Dec 2026), English-taught - provided Oct 2026) | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Seoul National University — South Korea</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>5271.321 Park and Open Space Planning (3 credits)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Fall 2026 (SNU 2nd semester, Sep-Dec) - English-taught</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Host: https://sugang.snu.ac.kr/ (SNU Course Search export, 2026 2nd semester (Fall, Sep-Dec 2026), English-taught - provided Oct 2026) | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>GEEP Environment and Planning (5 ECTS)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2b 2026-27</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEEP | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>2026-27 catalogue (term set at registration)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/ENVR | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM NOT VERIFIED: Not in Fall 2026 schedule; Spring 2027 schedule not yet published (HKUST takes either semester) [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>University of Groningen — Netherlands</t>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -1030,7 +1085,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1040,12 +1095,12 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>GEGIS Geographic Information Systems (10 ECTS)</t>
+          <t>ENVR3410 Economics for Environmental Policy and Management (3 credits)</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -1055,131 +1110,131 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Semester 2b 2026-27</t>
+          <t>Fall 2026 - HKUST takes students in either semester</t>
         </is>
       </c>
       <c r="I5" s="6" t="n"/>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEGIS | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/ENVR | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM VERIFIED Oct 2026: Fall 2026 - HKUST takes students in either semester [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>GEGPLEU Geography, Planning and European Union (5 ECTS)</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2a 2026-27</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEGPLEU | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>SOSC2299 The Rise and Fall of Globalization (3 credits)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>2026-27 catalogue (term set at registration)</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/SOSC | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM NOT VERIFIED: Not in Fall 2026 schedule; Spring 2027 schedule not yet published (HKUST takes either semester) [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>GEPOPGEO Population Geographies (10 ECTS)</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2a 2026-27</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEPOPGEO | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>SOSC2330 Environmental Politics and Policy (3 credits)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2026-27 catalogue (term set at registration)</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/SOSC | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM NOT VERIFIED: Not in Fall 2026 schedule; Spring 2027 schedule not yet published (HKUST takes either semester) [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>University of Groningen — Netherlands</t>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -1189,7 +1244,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>SOES220 CITIES AND REGIONS</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1199,12 +1254,12 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>GERG Rural Geography (5 ECTS)</t>
+          <t>SOSC2740 Gender and Society (3 credits)</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1214,447 +1269,924 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Semester 2b 2026-27</t>
+          <t>Fall 2026 - HKUST takes students in either semester</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="6" t="inlineStr">
         <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/SOSC | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM VERIFIED Oct 2026: Fall 2026 - HKUST takes students in either semester [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>SOSC3250 Gender and Development (3 credits)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2026-27 catalogue (term set at registration)</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/SOSC | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM NOT VERIFIED: Not in Fall 2026 schedule; Spring 2027 schedule not yet published (HKUST takes either semester) [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>SOSC3880 Social Inequality and Social Mobility (3 credits)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>2026-27 catalogue (term set at registration)</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/SOSC | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM NOT VERIFIED: Not in Fall 2026 schedule; Spring 2027 schedule not yet published (HKUST takes either semester) [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Seoul National University — South Korea</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>208.407A The Politics of Space and Geopolitics (3 credits)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Fall 2026 (SNU 2nd semester, Sep-Dec) - English-taught</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Host: https://sugang.snu.ac.kr/ (SNU Course Search export, 2026 2nd semester (Fall, Sep-Dec 2026), English-taught - provided Oct 2026) | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Seoul National University — South Korea</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>5271.321 Park and Open Space Planning (3 credits)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Fall 2026 (SNU 2nd semester, Sep-Dec) - English-taught</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Host: https://sugang.snu.ac.kr/ (SNU Course Search export, 2026 2nd semester (Fall, Sep-Dec 2026), English-taught - provided Oct 2026) | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>GEEP Environment and Planning (5 ECTS)</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Semester 2b 2026-27</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEEP | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>GEGIS Geographic Information Systems (10 ECTS)</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Semester 2b 2026-27</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEGIS | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>GEGPLEU Geography, Planning and European Union (5 ECTS)</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Semester 2a 2026-27</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEGPLEU | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>GEPOPGEO Population Geographies (10 ECTS)</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Semester 2a 2026-27</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEPOPGEO | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>SOES220 CITIES AND REGIONS</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>GERG Rural Geography (5 ECTS)</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Semester 2b 2026-27</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
           <t>Host: https://ocasys.rug.nl/current/catalog/course/GERG | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>University of Groningen — Netherlands</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>GESPSP2 Spatial Problems and Spatial Policies: The Dutch Experience (10 ECTS)</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Semester 2 2026-27 (exchange course)</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>Host: https://ocasys.rug.nl/current/catalog/course/GESPSP2 | NEW (catalogue search to fill gap, Oct 2026) | Course designed for FSS exchange students | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Course designed for FSS exchange students</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>University of Groningen — Netherlands</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>UCG3HU08 The City (5 ECTS)</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Semester 2b 2026-27</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>Host: https://ocasys.rug.nl/current/catalog/course/UCG3HU08 | NEW (catalogue search to fill gap, Oct 2026) | University College Groningen - check exchange access | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; University College Groningen - check exchange access</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam — Netherlands</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>E_EBE2_ETE Environmental and Transport Economics (6 EC)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Period 5 (Semester 2) 2026-27; taught in English</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/E_EBE2_ETE | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam — Netherlands</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>E_EBE3_IGS Inclusive Growth and Sustainability (6 EC)</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Period 5 (Semester 2) 2026-27; exchange course</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/E_EBE3_IGS | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam — Netherlands</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>L_AABACIW206 Globalisation and Localisation (6 EC)</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Period 5 (Semester 2) 2026-27; exchange course</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/L_AABACIW206 | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam — Netherlands</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>L_AABAMKD207 Urban Culture and Public Space (6 EC)</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Period 5 (Semester 2) 2026-27; exchange course</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/L_AABAMKD207 | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam — Netherlands</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>L_AABAMKD222 Mediating Environments (6 EC)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Period 4 (Semester 2) 2026-27; taught in English</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/L_AABAMKD222 | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam — Netherlands</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>S_HDSD The Human Dimension of Sustainable Development: From Ideal to Reality (6 EC)</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Period 5 (Semester 2) 2026-27; exchange course</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/S_HDSD | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1682,693 +2214,693 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>University name and country</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Programme title</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>UoL module code and title</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>UoL module level</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Host uni module code and title</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Host uni module level</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Core or optional</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Semester</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>CB approval</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Evidence / source URL</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Check notes (Oct 2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Seoul National University — South Korea</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>3345.312 Geochemistry and Lab. (3 credits)</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Fall 2026 (SNU 2nd semester, Sep-Dec) - English-taught</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Host: https://sugang.snu.ac.kr/ (SNU Course Search export, 2026 2nd semester (Fall, Sep-Dec 2026), English-taught - provided Oct 2026) | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Seoul National University — South Korea</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>457.210A Environmental Engineering (section 002, English) (3 credits)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>Fall 2026 (SNU 2nd semester, Sep-Dec) - English-taught</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Host: https://sugang.snu.ac.kr/ (SNU Course Search export, 2026 2nd semester (Fall, Sep-Dec 2026), English-taught - provided Oct 2026) | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>University of Groningen — Netherlands</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>GEEE Environment and Engineering (5 ECTS)</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Semester 2a 2026-27</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Host: https://ocasys.rug.nl/current/catalog/course/GEEE | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>University of Groningen — Netherlands</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>GEEP Environment and Planning (5 ECTS)</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Semester 2b 2026-27</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>Host: https://ocasys.rug.nl/current/catalog/course/GEEP | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>University of Groningen — Netherlands</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>GEGIS Geographic Information Systems (10 ECTS)</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Semester 2b 2026-27</t>
         </is>
       </c>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>Host: https://ocasys.rug.nl/current/catalog/course/GEGIS | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>University of Groningen — Netherlands</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>GELSC Landscapes (5 ECTS)</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Semester 2b 2026-27</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>Host: https://ocasys.rug.nl/current/catalog/course/GELSC | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>University of Groningen — Netherlands</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>GEPG Physical Geography (5 ECTS)</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Semester 2a 2026-27</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>Host: https://ocasys.rug.nl/current/catalog/course/GEPG | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>University of Groningen — Netherlands</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>WBBIP02-06 Artificial Intelligence for Forest and Landscape Remote Sensing (6 ECTS)</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Semester 2a 2026-27</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Host: https://ocasys.rug.nl/current/catalog/course/WBBIP02-06 | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Science and Engineering | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Science and Engineering</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam — Netherlands</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>AB_1201 Statistics and Methodology (6 EC)</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Period 4 (Semester 2) 2026-27; exchange course</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/AB_1201 | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam — Netherlands</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>AB_1288 Big Data in Sustainability Science (6 EC)</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Period 4 (Semester 2) 2026-27</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/AB_1288 | NEW (catalogue search to fill gap, Oct 2026) | Bachelor course not flagged as exchange course - confirm access | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Bachelor course not flagged as exchange course - confirm access</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam — Netherlands</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>AB_1357 Planetary Health: PHIACW (6 EC)</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Period 5 (Semester 2) 2026-27</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/AB_1357 | NEW (catalogue search to fill gap, Oct 2026) | Bachelor course not flagged as exchange course - confirm access | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Bachelor course not flagged as exchange course - confirm access</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam — Netherlands</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>AB_470074 Urban Ecology (6 EC)</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Period 6 (Semester 2) 2026-27</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/AB_470074 | NEW (catalogue search to fill gap, Oct 2026) | Bachelor course not flagged as exchange course - confirm access | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Bachelor course not flagged as exchange course - confirm access</t>
         </is>
@@ -2386,7 +2918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2403,541 +2935,997 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>University name and country</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Programme title</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>UoL module code and title</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>UoL module level</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Host uni module code and title</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Host uni module level</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Core or optional</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Semester</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>CB approval</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Evidence / source URL</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Why removed</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>SOSC3130 Hong Kong Culture (3 credits)</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>Fall 2026 - HKUST takes students in either semester</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/SOSC | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; NOT USABLE (language of tuition): Taught in Cantonese — Medium of instruction: Cantonese; requires Chinese reading - not usable [https://w5.ab.ust.hk/wcq/cgi-bin/2610/subject/SOSC]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>University of Groningen — Netherlands</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>GEECOGEO Economic Geography (10 ECTS)</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Semester 1b</t>
         </is>
       </c>
-      <c r="I2" s="7" t="n"/>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Host: https://ocasys.rug.nl/current/catalog/course/GEECOGEO | UoL: https://www.liverpool.ac.uk/courses/geography-ba-hons</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Original row; Wrong term for partner semester (Semester 2)</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>GESP1 Urbanism and Planning (10 ECTS)</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Semester 1a</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEECOGEO | UoL: https://www.liverpool.ac.uk/courses/geography-ba-hons</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Original row; Wrong term for partner semester (Semester 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>GEIGSDS Introduction to Geospatial Data Science (5 ECTS)</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Semester 1a (minor restriction)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEECOGEO | UoL: https://www.liverpool.ac.uk/courses/geography-bsc-hons</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Original row; Wrong term for partner semester (Semester 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>AB_1318 Land Use and Planning</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Period 5 (Semester 2) 2026-27</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/exchange/2026-2027 | UoL: https://www.liverpool.ac.uk/courses/geography-ba-hons</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Original row; Verified Oct 2026: Period 5 (Semester 2) 2026-27 - verified Oct 2026; NOT USABLE (language of tuition): Taught in Dutch — Language of tuition: Dutch - not usable (checked manually Oct 2026) [https://studiegids.vu.nl/en/courses/2026-2027/AB_1318]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>AM_1135 Methods of Environment and Resource Management</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>2026/27 exchange guide verified; exact period not publicly retrievable</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/exchange/2026-2027 | UoL: https://www.liverpool.ac.uk/courses/geography-ba-hons</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>Original row; Verified Oct 2026: Period 4 (Semester 2) - MASTER-level course; verified Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>AB_1271 GIS and Earth Observation</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Period 4 (Semester 2) 2026-27</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/exchange/2026-2027 | UoL: https://www.liverpool.ac.uk/courses/geography-bsc-hons</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>Original row; Verified Oct 2026: Period 4 (Semester 2) 2026-27 - verified Oct 2026; NOT USABLE (language of tuition): Taught in Dutch — Language of tuition: Dutch - not usable [https://studiegids.vu.nl/en/courses/2026-2027/AB_1271]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>AM_1183 Imaging and Assessing Landscapes</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>2026/27 exchange guide verified; exact period not publicly retrievable</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/exchange/2026-2027 | UoL: https://www.liverpool.ac.uk/courses/geography-bsc-hons</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>Original row; Verified Oct 2026: Period 4 (Semester 2) - MASTER-level course; verified Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>SOES214 CHANGING ENVIRONMENTS</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>AM_1197 Advanced Spatial Analyses</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>2026/27 exchange guide verified; exact period not publicly retrievable</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/exchange/2026-2027 | UoL: https://www.liverpool.ac.uk/courses/geography-bsc-hons</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>Original row; Verified Oct 2026: Period 2 (Semester 1) only - wrong term; MASTER-level; verified Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>E_STR_GIS Geographical Information Systems</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>2026/27 exchange guide verified; exact period not publicly retrievable</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/exchange/2026-2027 | UoL: https://www.liverpool.ac.uk/courses/geography-bsc-hons</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>Original row; Verified Oct 2026: Period 2 (Semester 1) only - wrong term; MASTER-level; verified Oct 2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>University name and country</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Programme title</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>UoL module code and title</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>UoL module level</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Host uni module code and title</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Host uni module level</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Core or optional</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>CB approval</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Evidence / source URL</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Check notes (Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>ENVR2060 From Trash to Treasure: Transforming Waste into Resources (3 credits)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>2026-27 catalogue (term set at registration)</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/ENVR | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM NOT VERIFIED: Not in Fall 2026 schedule; Spring 2027 schedule not yet published (HKUST takes either semester) [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>GESP1 Urbanism and Planning (10 ECTS)</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>Undergraduate</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Semester 1a</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="n"/>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEECOGEO | UoL: https://www.liverpool.ac.uk/courses/geography-ba-hons</t>
-        </is>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>Original row; Wrong term for partner semester (Semester 2)</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>ENVR3005 Environmental Risks: Principles and Practices (3 credits)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2026-27 catalogue (term set at registration)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/ENVR | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM NOT VERIFIED: Not in Fall 2026 schedule; Spring 2027 schedule not yet published (HKUST takes either semester) [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>GEIGSDS Introduction to Geospatial Data Science (5 ECTS)</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Undergraduate</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Semester 1a (minor restriction)</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEECOGEO | UoL: https://www.liverpool.ac.uk/courses/geography-bsc-hons</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>Original row; Wrong term for partner semester (Semester 2)</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>SOSC2299 The Rise and Fall of Globalization (3 credits)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>2026-27 catalogue (term set at registration)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/SOSC | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM NOT VERIFIED: Not in Fall 2026 schedule; Spring 2027 schedule not yet published (HKUST takes either semester) [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>AB_1318 Land Use and Planning</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Period 5 (Semester 2) 2026-27</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/exchange/2026-2027 | UoL: https://www.liverpool.ac.uk/courses/geography-ba-hons</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>Original row; Verified Oct 2026: Period 5 (Semester 2) 2026-27 - verified Oct 2026; NOT USABLE (language of tuition): Taught in Dutch — Language of tuition: Dutch - not usable (checked manually Oct 2026) [https://studiegids.vu.nl/en/courses/2026-2027/AB_1318]</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>SOSC2330 Environmental Politics and Policy (3 credits)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2026-27 catalogue (term set at registration)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/SOSC | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM NOT VERIFIED: Not in Fall 2026 schedule; Spring 2027 schedule not yet published (HKUST takes either semester) [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>AM_1135 Methods of Environment and Resource Management</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>2026/27 exchange guide verified; exact period not publicly retrievable</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/exchange/2026-2027 | UoL: https://www.liverpool.ac.uk/courses/geography-ba-hons</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>Original row; Verified Oct 2026: Period 4 (Semester 2) - MASTER-level course; verified Oct 2026</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>SOSC3250 Gender and Development (3 credits)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>2026-27 catalogue (term set at registration)</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/SOSC | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM NOT VERIFIED: Not in Fall 2026 schedule; Spring 2027 schedule not yet published (HKUST takes either semester) [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>AB_1271 GIS and Earth Observation</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Period 4 (Semester 2) 2026-27</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/exchange/2026-2027 | UoL: https://www.liverpool.ac.uk/courses/geography-bsc-hons</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>Original row; Verified Oct 2026: Period 4 (Semester 2) 2026-27 - verified Oct 2026; NOT USABLE (language of tuition): Taught in Dutch — Language of tuition: Dutch - not usable [https://studiegids.vu.nl/en/courses/2026-2027/AB_1271]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>AM_1183 Imaging and Assessing Landscapes</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>2026/27 exchange guide verified; exact period not publicly retrievable</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/exchange/2026-2027 | UoL: https://www.liverpool.ac.uk/courses/geography-bsc-hons</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>Original row; Verified Oct 2026: Period 4 (Semester 2) - MASTER-level course; verified Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>AM_1197 Advanced Spatial Analyses</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>2026/27 exchange guide verified; exact period not publicly retrievable</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/exchange/2026-2027 | UoL: https://www.liverpool.ac.uk/courses/geography-bsc-hons</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>Original row; Verified Oct 2026: Period 2 (Semester 1) only - wrong term; MASTER-level; verified Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>E_STR_GIS Geographical Information Systems</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Undergraduate</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>2026/27 exchange guide verified; exact period not publicly retrievable</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/exchange/2026-2027 | UoL: https://www.liverpool.ac.uk/courses/geography-bsc-hons</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>Original row; Verified Oct 2026: Period 2 (Semester 1) only - wrong term; MASTER-level; verified Oct 2026</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology — Hong Kong (SAR)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>SOSC3880 Social Inequality and Social Mobility (3 credits)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2026-27 catalogue (term set at registration)</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Host: https://prog-crs.hkust.edu.hk/ugcourse/2026-27/SOSC | NEW (Jul 2025 handbook, not previously in this file) - verified in current host catalogue, Oct 2026 | UoL match is a SUGGESTION for department review (programme LOs, not close module match)</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: July 2025 handbook module verified in current catalogue; UoL match is a suggestion for review; TERM NOT VERIFIED: Not in Fall 2026 schedule; Spring 2027 schedule not yet published (HKUST takes either semester) [https://w5.ab.ust.hk/wcq/cgi-bin/2610/]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/curriculum_mapping_2026-27/CurriculumMapping_Geo_4_To_check.xlsx
+++ b/curriculum_mapping_2026-27/CurriculumMapping_Geo_4_To_check.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Updated 5 Oct 2026 (deep check). Only modules running in the partner exchange period count: UoL Semester 1 partners = Fall 2026 / Term 1 / Semester A; UoL Semester 2 partners = Semester 1 2027 (Australia), Trimester 1 2027 (Wellington), Semester 2 2026-27 (Netherlands); XJTLU, HKUST, SNU and Calgary accept either semester. Amber rows = term could not be verified (timetable behind login / captcha / not yet published). Green rows = modules added Oct 2026 from the 2026/27 timetables. UoL matches on added rows are suggestions for department review.</t>
+          <t>Updated 5 Oct 2026 (deep check). Only modules running in the partner exchange period count: UoL Semester 1 partners = Fall 2026 / Term 1 / Semester A; UoL Semester 2 partners = Semester 1 2027 (Australia), Trimester 1 2027 (Wellington), Semester 2 2026-27 (Netherlands); XJTLU, HKUST, SNU and Calgary accept either semester. Amber rows = term could not be verified (timetable behind login / captcha / not yet published). Green rows = modules added Oct 2026 from the 2026/27 timetables. Lilac rows = term INFERRED from previous years or the usual offering pattern (TERM LIKELY / TERM FROM PREVIOUS YEAR) because the 2026/27 timetable is not yet published - confirm when available. UoL matches on added rows are suggestions for department review.</t>
         </is>
       </c>
     </row>

--- a/curriculum_mapping_2026-27/CurriculumMapping_Geo_4_To_check.xlsx
+++ b/curriculum_mapping_2026-27/CurriculumMapping_Geo_4_To_check.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Fall 2026 (SNU 2nd semester) checked from the SNU course list: the Geography Department offers only ONE English-taught undergraduate course (208.407A The Politics of Space and Geopolitics); all other geography courses, including the handbook ones (208.302 Geography of Korea, 208.421A History of Geographical Space and Thoughts, 205.242A Population Change and Aging Society), are taught in Korean. 2 English-taught usable modules found, 4 needed -&gt; NOT enough for Fall 2026. Spring 2027 (1st semester) list not yet checked.</t>
+          <t>Fall 2026 (SNU 2nd semester) checked from the SNU course list: the Geography Department offers only ONE English-taught undergraduate course (208.407A The Politics of Space and Geopolitics); all other geography courses, including the handbook ones (208.302 Geography of Korea, 208.421A History of Geographical Space and Thoughts, 205.242A Population Change and Aging Society), are taught in Korean. 2 English-taught usable modules found, 4 needed -&gt; NOT enough for Fall 2026. SPRING evidence (UCEAP / UT Austin exchange records + LikeSNU last-offered semester): 208.228A Geography of Population Change and Migration (English, last offered Spring 2025) and 208.321 Field Study in Geography (English, last offered Spring 2025) - at most 2 English geography courses in Spring; other Spring 2026 geography courses (208.207 Urban Geography, 208.219 Intro Physical Geography, 208.328 Environmental Hazards and Society) have no evidence of English teaching. Not enough English Geography provision in either semester without SNU confirmation.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Fall 2026 (SNU 2nd semester) checked from the SNU course list: the Geography Department offers only ONE English-taught undergraduate course (208.407A The Politics of Space and Geopolitics); all other geography courses, including the handbook ones (208.302 Geography of Korea, 208.421A History of Geographical Space and Thoughts, 205.242A Population Change and Aging Society), are taught in Korean. 2 English-taught usable modules found, 4 needed -&gt; NOT enough for Fall 2026. Spring 2027 (1st semester) list not yet checked.</t>
+          <t>Fall 2026 (SNU 2nd semester) checked from the SNU course list: the Geography Department offers only ONE English-taught undergraduate course (208.407A The Politics of Space and Geopolitics); all other geography courses, including the handbook ones (208.302 Geography of Korea, 208.421A History of Geographical Space and Thoughts, 205.242A Population Change and Aging Society), are taught in Korean. 2 English-taught usable modules found, 4 needed -&gt; NOT enough for Fall 2026. SPRING evidence (UCEAP / UT Austin exchange records + LikeSNU last-offered semester): 208.228A Geography of Population Change and Migration (English, last offered Spring 2025) and 208.321 Field Study in Geography (English, last offered Spring 2025) - at most 2 English geography courses in Spring; other Spring 2026 geography courses (208.207 Urban Geography, 208.219 Intro Physical Geography, 208.328 Environmental Hazards and Society) have no evidence of English teaching. Not enough English Geography provision in either semester without SNU confirmation.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">

--- a/curriculum_mapping_2026-27/CurriculumMapping_Geo_4_To_check.xlsx
+++ b/curriculum_mapping_2026-27/CurriculumMapping_Geo_4_To_check.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Rows removed (not usable)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geography BA'!$A$1:$K$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Geography BSc'!$A$1:$K$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Geography BA'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Geography BSc'!$A$1:$K$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rows removed (not usable)'!$A$1:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9F2D0"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00D9F2D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Seoul National University</t>
+          <t>University of Groningen</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -564,35 +564,35 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Fall 2026 (SNU 2nd semester) checked from the SNU course list: the Geography Department offers only ONE English-taught undergraduate course (208.407A The Politics of Space and Geopolitics); all other geography courses, including the handbook ones (208.302 Geography of Korea, 208.421A History of Geographical Space and Thoughts, 205.242A Population Change and Aging Society), are taught in Korean. 2 English-taught usable modules found, 4 needed -&gt; NOT enough for Fall 2026. SPRING evidence (UCEAP / UT Austin exchange records + LikeSNU last-offered semester): 208.228A Geography of Population Change and Migration (English, last offered Spring 2025) and 208.321 Field Study in Geography (English, last offered Spring 2025) - at most 2 English geography courses in Spring; other Spring 2026 geography courses (208.207 Urban Geography, 208.219 Intro Physical Geography, 208.328 Environmental Hazards and Society) have no evidence of English teaching. Not enough English Geography provision in either semester without SNU confirmation.</t>
+          <t>Faculty access: confirmed list says UoL students apply to Faculty of Arts / Science and Engineering, but most usable modules are Faculty of Spatial Sciences (FSS does run an exchange course, GESPSP2). Confirm with Study Abroad. Also the workbook's original Groningen rows are Semester 1 (wrong term).</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Spring Semester 1 (Mar-Jun - UoL Semester 2) OR Fall Semester 2 (Sep-Dec - UoL Semester 1)</t>
+          <t>Semester 2</t>
         </is>
       </c>
       <c r="H5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Seoul National University</t>
+          <t>University of Groningen</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -601,35 +601,35 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Fall 2026 (SNU 2nd semester) checked from the SNU course list: the Geography Department offers only ONE English-taught undergraduate course (208.407A The Politics of Space and Geopolitics); all other geography courses, including the handbook ones (208.302 Geography of Korea, 208.421A History of Geographical Space and Thoughts, 205.242A Population Change and Aging Society), are taught in Korean. 2 English-taught usable modules found, 4 needed -&gt; NOT enough for Fall 2026. SPRING evidence (UCEAP / UT Austin exchange records + LikeSNU last-offered semester): 208.228A Geography of Population Change and Migration (English, last offered Spring 2025) and 208.321 Field Study in Geography (English, last offered Spring 2025) - at most 2 English geography courses in Spring; other Spring 2026 geography courses (208.207 Urban Geography, 208.219 Intro Physical Geography, 208.328 Environmental Hazards and Society) have no evidence of English teaching. Not enough English Geography provision in either semester without SNU confirmation.</t>
+          <t>Faculty access: confirmed list says UoL students apply to Faculty of Arts / Science and Engineering, but most usable modules are Faculty of Spatial Sciences (FSS does run an exchange course, GESPSP2). Confirm with Study Abroad. Also the workbook's original Groningen rows are Semester 1 (wrong term).</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Spring Semester 1 (Mar-Jun - UoL Semester 2) OR Fall Semester 2 (Sep-Dec - UoL Semester 1)</t>
+          <t>Semester 2</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>University of Groningen</t>
+          <t>Vrije Universiteit Amsterdam</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -638,17 +638,17 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Faculty access: confirmed list says UoL students apply to Faculty of Arts / Science and Engineering, but most usable modules are Faculty of Spatial Sciences (FSS does run an exchange course, GESPSP2). Confirm with Study Abroad. Also the workbook's original Groningen rows are Semester 1 (wrong term).</t>
+          <t>6 English-taught modules in Semester 2 (P4-P6), 5 needed (30 EC). AB_1318 and AB_1271 removed: taught in Dutch (all other rows checked: English). Minimum met. Confirm exchange access with VU International Office.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>2</v>
@@ -666,7 +666,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>University of Groningen</t>
+          <t>Vrije Universiteit Amsterdam</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -675,17 +675,17 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Faculty access: confirmed list says UoL students apply to Faculty of Arts / Science and Engineering, but most usable modules are Faculty of Spatial Sciences (FSS does run an exchange course, GESPSP2). Confirm with Study Abroad. Also the workbook's original Groningen rows are Semester 1 (wrong term).</t>
+          <t>4 English-taught modules in Semester 2 (P4-P6), 5 needed (30 EC). AB_1318 and AB_1271 removed: taught in Dutch (all other rows checked: English). NOT enough - short by 1. Confirm exchange access with VU International Office.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -694,83 +694,9 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>6 English-taught modules in Semester 2 (P4-P6), 5 needed (30 EC). AB_1318 and AB_1271 removed: taught in Dutch (all other rows checked: English). Minimum met. Confirm exchange access with VU International Office.</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>4 English-taught modules in Semester 2 (P4-P6), 5 needed (30 EC). AB_1318 and AB_1271 removed: taught in Dutch (all other rows checked: English). NOT enough - short by 1. Confirm exchange access with VU International Office.</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Semester 2</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -785,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -861,7 +787,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Seoul National University — South Korea</t>
+          <t>University of Groningen — Netherlands</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -871,7 +797,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -881,12 +807,12 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>208.407A The Politics of Space and Geopolitics (3 credits)</t>
+          <t>GEEP Environment and Planning (5 ECTS)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Bachelor</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -896,25 +822,25 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Fall 2026 (SNU 2nd semester, Sep-Dec) - English-taught</t>
+          <t>Semester 2b 2026-27</t>
         </is>
       </c>
       <c r="I2" s="5" t="n"/>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Host: https://sugang.snu.ac.kr/ (SNU Course Search export, 2026 2nd semester (Fall, Sep-Dec 2026), English-taught - provided Oct 2026) | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEEP | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Seoul National University — South Korea</t>
+          <t>University of Groningen — Netherlands</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -924,7 +850,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -934,12 +860,12 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>5271.321 Park and Open Space Planning (3 credits)</t>
+          <t>GEGIS Geographic Information Systems (10 ECTS)</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Bachelor</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -949,290 +875,290 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Fall 2026 (SNU 2nd semester, Sep-Dec) - English-taught</t>
+          <t>Semester 2b 2026-27</t>
         </is>
       </c>
       <c r="I3" s="5" t="n"/>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Host: https://sugang.snu.ac.kr/ (SNU Course Search export, 2026 2nd semester (Fall, Sep-Dec 2026), English-taught - provided Oct 2026) | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEGIS | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>University of Groningen — Netherlands</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>GEEP Environment and Planning (5 ECTS)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>GEGPLEU Geography, Planning and European Union (5 ECTS)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Semester 2a 2026-27</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEGPLEU | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>GEPOPGEO Population Geographies (10 ECTS)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Semester 2a 2026-27</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEPOPGEO | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>SOES220 CITIES AND REGIONS</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>GERG Rural Geography (5 ECTS)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Semester 2b 2026-27</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEEP | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GERG | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>University of Groningen — Netherlands</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>SOES277 GIS FOR SOCIAL SCIENCES</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>GEGIS Geographic Information Systems (10 ECTS)</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>GESPSP2 Spatial Problems and Spatial Policies: The Dutch Experience (10 ECTS)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Bachelor</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Semester 2 2026-27 (exchange course)</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GESPSP2 | NEW (catalogue search to fill gap, Oct 2026) | Course designed for FSS exchange students | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Course designed for FSS exchange students</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>UCG3HU08 The City (5 ECTS)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Semester 2b 2026-27</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEGIS | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>GEGPLEU Geography, Planning and European Union (5 ECTS)</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2a 2026-27</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEGPLEU | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>GEPOPGEO Population Geographies (10 ECTS)</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2a 2026-27</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEPOPGEO | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>SOES220 CITIES AND REGIONS</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>GERG Rural Geography (5 ECTS)</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2b 2026-27</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GERG | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/UCG3HU08 | NEW (catalogue search to fill gap, Oct 2026) | University College Groningen - check exchange access | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; University College Groningen - check exchange access</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>University of Groningen — Netherlands</t>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1242,7 +1168,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>SOES222 PLANNING FOR SUSTAINABLE URBANISM</t>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1252,12 +1178,12 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>GESPSP2 Spatial Problems and Spatial Policies: The Dutch Experience (10 ECTS)</t>
+          <t>E_EBE2_ETE Environmental and Transport Economics (6 EC)</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Bachelor</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1267,71 +1193,71 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Semester 2 2026-27 (exchange course)</t>
+          <t>Period 5 (Semester 2) 2026-27; taught in English</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GESPSP2 | NEW (catalogue search to fill gap, Oct 2026) | Course designed for FSS exchange students | UoL match is a SUGGESTION for department review</t>
+          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/E_EBE2_ETE | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Course designed for FSS exchange students</t>
+          <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>UCG3HU08 The City (5 ECTS)</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2b 2026-27</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/UCG3HU08 | NEW (catalogue search to fill gap, Oct 2026) | University College Groningen - check exchange access | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; University College Groningen - check exchange access</t>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>E_EBE3_IGS Inclusive Growth and Sustainability (6 EC)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Period 5 (Semester 2) 2026-27; exchange course</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/E_EBE3_IGS | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1274,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
+          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1358,12 +1284,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>E_EBE2_ETE Environmental and Transport Economics (6 EC)</t>
+          <t>L_AABACIW206 Globalisation and Localisation (6 EC)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1373,69 +1299,69 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Period 5 (Semester 2) 2026-27; taught in English</t>
+          <t>Period 5 (Semester 2) 2026-27; exchange course</t>
         </is>
       </c>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/E_EBE2_ETE | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
+          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/L_AABACIW206 | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Vrije Universiteit Amsterdam — Netherlands</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Geography BA</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>SOES224 POLITICAL ECONOMIES OF CRISIS AND CHANGE</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>E_EBE3_IGS Inclusive Growth and Sustainability (6 EC)</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>L_AABAMKD207 Urban Culture and Public Space (6 EC)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Period 5 (Semester 2) 2026-27; exchange course</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/E_EBE3_IGS | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/L_AABAMKD207 | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
         </is>
@@ -1454,7 +1380,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>SOES275 SOCIAL AND CULTURAL GEOGRAPHIES</t>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1464,7 +1390,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>L_AABACIW206 Globalisation and Localisation (6 EC)</t>
+          <t>L_AABAMKD222 Mediating Environments (6 EC)</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1479,182 +1405,76 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Period 5 (Semester 2) 2026-27; exchange course</t>
+          <t>Period 4 (Semester 2) 2026-27; taught in English</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/L_AABACIW206 | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
+          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/L_AABAMKD222 | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
+          <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Geography BA</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>S_HDSD The Human Dimension of Sustainable Development: From Ideal to Reality (6 EC)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Period 5 (Semester 2) 2026-27; exchange course</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/S_HDSD | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>SOES225 THEMES IN URBAN GEOGRAPHY</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>L_AABAMKD207 Urban Culture and Public Space (6 EC)</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Period 5 (Semester 2) 2026-27; exchange course</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/L_AABAMKD207 | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>L_AABAMKD222 Mediating Environments (6 EC)</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Period 4 (Semester 2) 2026-27; taught in English</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/L_AABAMKD222 | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Geography BA</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>SOES270 RETHINKING NATURE: ENVIRONMENTAL KNOWLEDGE, SCIENCE AND SOCIETY</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>S_HDSD The Human Dimension of Sustainable Development: From Ideal to Reality (6 EC)</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Period 5 (Semester 2) 2026-27; exchange course</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/S_HDSD | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K16"/>
+  <autoFilter ref="A1:K14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1665,7 +1485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1741,7 +1561,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Seoul National University — South Korea</t>
+          <t>University of Groningen — Netherlands</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -1761,12 +1581,12 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>3345.312 Geochemistry and Lab. (3 credits)</t>
+          <t>GEEE Environment and Engineering (5 ECTS)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Bachelor</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1776,25 +1596,25 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Fall 2026 (SNU 2nd semester, Sep-Dec) - English-taught</t>
+          <t>Semester 2a 2026-27</t>
         </is>
       </c>
       <c r="I2" s="5" t="n"/>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Host: https://sugang.snu.ac.kr/ (SNU Course Search export, 2026 2nd semester (Fall, Sep-Dec 2026), English-taught - provided Oct 2026) | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEEE | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Seoul National University — South Korea</t>
+          <t>University of Groningen — Netherlands</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -1814,12 +1634,12 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>457.210A Environmental Engineering (section 002, English) (3 credits)</t>
+          <t>GEEP Environment and Planning (5 ECTS)</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Bachelor</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1829,553 +1649,447 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Fall 2026 (SNU 2nd semester, Sep-Dec) - English-taught</t>
+          <t>Semester 2b 2026-27</t>
         </is>
       </c>
       <c r="I3" s="5" t="n"/>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Host: https://sugang.snu.ac.kr/ (SNU Course Search export, 2026 2nd semester (Fall, Sep-Dec 2026), English-taught - provided Oct 2026) | NEW (Oct 2026 deep check: module confirmed in the 2026/27 timetable for the exchange period) | UoL match is a SUGGESTION for department review</t>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEEP | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Added Oct 2026 (deep check): verified in 2026/27 timetable; UoL match is a suggestion for review</t>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>University of Groningen — Netherlands</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>GEGIS Geographic Information Systems (10 ECTS)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Semester 2b 2026-27</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEGIS | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>GELSC Landscapes (5 ECTS)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Semester 2b 2026-27</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GELSC | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>GEPG Physical Geography (5 ECTS)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Semester 2a 2026-27</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEPG | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>University of Groningen — Netherlands</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>WBBIP02-06 Artificial Intelligence for Forest and Landscape Remote Sensing (6 ECTS)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Bachelor</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Semester 2a 2026-27</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://ocasys.rug.nl/current/catalog/course/WBBIP02-06 | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Science and Engineering | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Science and Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>AB_1201 Statistics and Methodology (6 EC)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Period 4 (Semester 2) 2026-27; exchange course</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/AB_1201 | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>AB_1288 Big Data in Sustainability Science (6 EC)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Period 4 (Semester 2) 2026-27</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/AB_1288 | NEW (catalogue search to fill gap, Oct 2026) | Bachelor course not flagged as exchange course - confirm access | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Bachelor course not flagged as exchange course - confirm access</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Geography BSc</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>GEEE Environment and Engineering (5 ECTS)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2a 2026-27</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEEE | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>AB_1357 Planetary Health: PHIACW (6 EC)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Period 5 (Semester 2) 2026-27</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/AB_1357 | NEW (catalogue search to fill gap, Oct 2026) | Bachelor course not flagged as exchange course - confirm access | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Bachelor course not flagged as exchange course - confirm access</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam — Netherlands</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Geography BSc</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>SOES214 CHANGING ENVIRONMENTS</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>GEEP Environment and Planning (5 ECTS)</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2b 2026-27</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEEP | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>GEGIS Geographic Information Systems (10 ECTS)</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2b 2026-27</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEGIS | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>GELSC Landscapes (5 ECTS)</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2b 2026-27</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GELSC | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>SOES218 GEOMORPHOLOGY: PROCESSES AND FORMS</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>GEPG Physical Geography (5 ECTS)</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2a 2026-27</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/GEPG | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Spatial Sciences - confirmed list says UoL students apply to Arts / Science and Engineering; FSS takes exchange students (see GESPSP2) - confirm with Study Abroad</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>University of Groningen — Netherlands</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>SOES269 GIS FOR THE NATURAL ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>WBBIP02-06 Artificial Intelligence for Forest and Landscape Remote Sensing (6 ECTS)</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Bachelor</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Semester 2a 2026-27</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://ocasys.rug.nl/current/catalog/course/WBBIP02-06 | NEW (catalogue search to fill gap, Oct 2026) | Faculty of Science and Engineering | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Faculty of Science and Engineering</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>AB_1201 Statistics and Methodology (6 EC)</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Period 4 (Semester 2) 2026-27; exchange course</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/AB_1201 | NEW (catalogue search to fill gap, Oct 2026) | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>SOES213 GEOGRAPHICAL DATA ANALYSIS AND PROCESSING</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>AB_1288 Big Data in Sustainability Science (6 EC)</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Period 4 (Semester 2) 2026-27</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/AB_1288 | NEW (catalogue search to fill gap, Oct 2026) | Bachelor course not flagged as exchange course - confirm access | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>AB_470074 Urban Ecology (6 EC)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Period 6 (Semester 2) 2026-27</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/AB_470074 | NEW (catalogue search to fill gap, Oct 2026) | Bachelor course not flagged as exchange course - confirm access | UoL match is a SUGGESTION for department review</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Bachelor course not flagged as exchange course - confirm access</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>AB_1357 Planetary Health: PHIACW (6 EC)</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Period 5 (Semester 2) 2026-27</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/AB_1357 | NEW (catalogue search to fill gap, Oct 2026) | Bachelor course not flagged as exchange course - confirm access | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Bachelor course not flagged as exchange course - confirm access</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Vrije Universiteit Amsterdam — Netherlands</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Geography BSc</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>SOES214 CHANGING ENVIRONMENTS</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>AB_470074 Urban Ecology (6 EC)</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Period 6 (Semester 2) 2026-27</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Host: https://studiegids.vu.nl/en/courses/2026-2027/AB_470074 | NEW (catalogue search to fill gap, Oct 2026) | Bachelor course not flagged as exchange course - confirm access | UoL match is a SUGGESTION for department review</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>Added Oct 2026: catalogue search to fill gap; UoL match is a suggestion for review; Bachelor course not flagged as exchange course - confirm access</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K13"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
